--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -694,14 +694,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -718,7 +717,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -728,8 +727,11 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="3" t="n">
-        <v/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -737,12 +739,15 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="n">
-        <v/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
@@ -754,8 +759,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12278
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -766,7 +770,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -777,13 +782,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -795,13 +800,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -831,7 +836,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -849,7 +854,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -873,43 +878,43 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8235
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
@@ -921,19 +926,19 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -945,7 +950,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -957,13 +962,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -999,7 +1004,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -1011,13 +1016,13 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1033,12 +1038,16 @@
 </t>
         </is>
       </c>
-      <c r="L6" s="3" t="n">
-        <v/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1055,13 +1064,13 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>471</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1084,13 +1093,13 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1102,12 +1111,15 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">578
+</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1147,7 +1159,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1159,15 +1171,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v/>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1177,43 +1186,44 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">54621561
+81
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11092
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">283412
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -1225,13 +1235,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1243,13 +1253,12 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1296,19 +1305,19 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1318,18 +1327,21 @@
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
-        <v/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1344,19 +1356,19 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1374,25 +1386,31 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">450
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1410,7 +1428,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11944
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1437,18 +1455,20 @@
           <t>1458</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1459,41 +1479,45 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">847
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1510,50 +1534,50 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>134</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>957</t>
+          <t xml:space="preserve">957
+</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1577,87 +1601,86 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1666,13 +1689,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1684,31 +1707,31 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1732,52 +1755,55 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
-        <v/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1861
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1789,45 +1815,45 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>484</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -1839,19 +1865,18 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1886,7 +1911,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1898,7 +1923,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1910,49 +1935,49 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1970,7 +1995,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1988,7 +2013,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2000,7 +2025,8 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2029,19 +2055,19 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2053,13 +2079,13 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2071,11 +2097,15 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -2085,64 +2115,64 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10660
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -2151,7 +2181,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2181,7 +2211,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2191,8 +2221,11 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
-        <v/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -2208,103 +2241,102 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2134
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2462
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11182
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1393
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2334,139 +2366,137 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1646
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2490,27 +2520,30 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v/>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1939
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2521,41 +2554,43 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">994
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2566,29 +2601,29 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2600,18 +2635,18 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t xml:space="preserve">933
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -2647,12 +2682,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2664,7 +2700,8 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">113
+61
 </t>
         </is>
       </c>
@@ -2676,8 +2713,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>007</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2692,30 +2728,32 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
-        <v/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2204
 </t>
         </is>
       </c>
@@ -2727,13 +2765,12 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2745,25 +2782,24 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2787,28 +2823,28 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -2819,91 +2855,94 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">060
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t xml:space="preserve">468
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>691</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t xml:space="preserve">469
+</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2062
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2926,99 +2965,100 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v/>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3030,7 +3070,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3042,19 +3082,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3078,7 +3118,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3090,37 +3130,37 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3132,19 +3172,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8810
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -3168,48 +3208,49 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">24654
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3233,132 +3274,131 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>64170</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3400,126 +3440,124 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1880
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">2678
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">7268
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -3555,120 +3593,118 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>348</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2850
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>711</t>
+          <t xml:space="preserve">1114
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">967
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
+          <t xml:space="preserve">12385
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v/>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -3692,7 +3728,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3704,25 +3740,25 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3734,7 +3770,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3746,18 +3782,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3769,24 +3806,25 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>804</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3798,31 +3836,31 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3844,8 +3882,11 @@
       <c r="C25" s="3" t="n">
         <v/>
       </c>
-      <c r="D25" s="3" t="n">
-        <v/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1456
+</t>
+        </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -3854,8 +3895,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3865,13 +3905,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3888,7 +3927,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3899,68 +3938,66 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>6054</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>6054</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -3990,84 +4027,88 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1309
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -4076,7 +4117,8 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -4093,13 +4135,13 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">144944
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -4111,13 +4153,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4141,81 +4183,87 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>4654</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11946
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4236,7 +4284,7 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4254,7 +4302,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4290,19 +4338,19 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4314,19 +4362,19 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4338,24 +4386,27 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -4365,7 +4416,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4377,49 +4428,49 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2956
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4449,13 +4500,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4473,7 +4524,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4485,24 +4536,24 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4538,7 +4589,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -4550,7 +4601,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12296
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4562,13 +4613,13 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4598,25 +4649,25 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
+          <t xml:space="preserve">13532
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">858
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -4626,7 +4677,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4637,7 +4688,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4649,28 +4700,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>417</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
+          <t xml:space="preserve">1391
 </t>
         </is>
       </c>
@@ -4682,42 +4734,44 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v/>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>964</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>346</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4740,7 +4794,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4752,7 +4806,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4764,13 +4818,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8106
-</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -4780,12 +4833,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4796,55 +4852,52 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
-</t>
-        </is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v/>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4856,19 +4909,19 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4892,7 +4945,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -4916,74 +4969,75 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1924
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4995,7 +5049,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5013,7 +5067,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5049,13 +5103,13 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5067,25 +5121,25 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -5103,25 +5157,25 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -5133,46 +5187,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5196,7 +5253,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5208,13 +5265,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5226,7 +5283,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5238,7 +5295,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -5250,19 +5307,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -5274,7 +5331,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5286,13 +5343,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">576
 </t>
         </is>
       </c>
@@ -5310,7 +5367,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5322,13 +5379,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5352,7 +5409,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5364,7 +5421,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5376,19 +5433,19 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -5400,7 +5457,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5410,12 +5467,15 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="n">
-        <v/>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">9006
 </t>
         </is>
       </c>
@@ -5427,13 +5487,13 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -5445,43 +5505,43 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -5505,7 +5565,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">486
 </t>
         </is>
       </c>
@@ -5517,13 +5577,13 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5535,49 +5595,48 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1726
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5589,13 +5648,13 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5607,12 +5666,15 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
@@ -5628,13 +5690,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
@@ -5658,7 +5720,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
@@ -5670,14 +5732,13 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5688,13 +5749,13 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -5705,79 +5766,81 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t xml:space="preserve">999
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
+          <t xml:space="preserve">1348
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">19228
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3868
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
@@ -5807,59 +5870,60 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18950
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">7
+9
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5871,7 +5935,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">7378
 </t>
         </is>
       </c>
@@ -5883,55 +5947,56 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">77
+248
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">117
+203
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>00578</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5967,25 +6032,25 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -6003,8 +6068,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -6015,84 +6079,85 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122084
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2394
+          <t xml:space="preserve">1354
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6128,26 +6193,25 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6158,48 +6222,48 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11262
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2616
 </t>
         </is>
       </c>
@@ -6211,43 +6275,43 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1354
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6271,34 +6335,37 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6310,7 +6377,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6322,55 +6389,55 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">8401
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -6379,25 +6446,25 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">765
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6421,55 +6488,55 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1708
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -6481,25 +6548,25 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
@@ -6517,39 +6584,45 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6577,18 +6650,18 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6599,25 +6672,25 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -6629,7 +6702,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6641,31 +6714,31 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -6677,7 +6750,7 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6689,18 +6762,21 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14270
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -6722,21 +6798,26 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -6746,95 +6827,97 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">11256
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1650
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>7650</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1470
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
@@ -6865,42 +6948,42 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -6912,91 +6995,90 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">9984
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>0526</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">1141
+41 1
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01111
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">3179
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v/>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7018,25 +7100,26 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">89
+6
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7058,12 +7141,15 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -7075,79 +7161,81 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">1141
+41 1
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">2919292795
+24
+12
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -677,20 +677,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -698,14 +707,23 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -716,11 +734,17 @@
       <c r="L4" s="3" t="n">
         <v/>
       </c>
-      <c r="M4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -728,12 +752,15 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="n">
-        <v/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1 39
+</t>
+        </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -743,14 +770,23 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
       </c>
       <c r="V4" s="3" t="n">
         <v/>
@@ -785,14 +821,23 @@
       <c r="C5" s="3" t="n">
         <v/>
       </c>
-      <c r="D5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -800,41 +845,65 @@
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11289
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830
+</t>
+        </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -842,12 +911,15 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -865,7 +937,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -905,8 +977,11 @@
       <c r="C6" s="3" t="n">
         <v/>
       </c>
-      <c r="D6" s="3" t="n">
-        <v/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -914,12 +989,14 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -929,66 +1006,87 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
-        <v/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1036,30 +1134,43 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -1069,35 +1180,52 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11186
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
       </c>
       <c r="P7" s="3" t="n">
         <v/>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
@@ -1107,8 +1235,11 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="3" t="n">
-        <v/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -1118,18 +1249,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1153,7 +1285,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -1161,45 +1293,60 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
         <v/>
       </c>
-      <c r="M8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
       </c>
       <c r="P8" s="3" t="n">
         <v/>
@@ -1210,8 +1357,11 @@
 </t>
         </is>
       </c>
-      <c r="R8" s="3" t="n">
-        <v/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
@@ -1221,28 +1371,31 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">450
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2258
+</t>
+        </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1275,34 +1428,44 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1428
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">824
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">346
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1313,20 +1476,25 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -1338,59 +1506,61 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19438
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10960
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">20991
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9926
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">2299
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">6150
 </t>
         </is>
       </c>
@@ -1414,123 +1584,138 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">113
+</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19438
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10960
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11026
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>2294610</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>9114</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1552,115 +1737,125 @@
       <c r="C11" s="3" t="n">
         <v/>
       </c>
-      <c r="D11" s="3" t="n">
-        <v/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1284
+</t>
+        </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">1184
+</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">8909
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v/>
       </c>
       <c r="V11" s="3" t="n">
         <v/>
       </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
+      <c r="W11" s="3" t="n">
+        <v/>
       </c>
       <c r="X11" s="3" t="n">
         <v/>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v/>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1677,58 +1872,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11820
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -1738,66 +1950,66 @@
 </t>
         </is>
       </c>
-      <c r="P12" s="3" t="n">
-        <v/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v/>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1971
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1816,118 +2028,144 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 1
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v/>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11820
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2835
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1949,84 +2187,105 @@
       <c r="C14" s="3" t="n">
         <v/>
       </c>
-      <c r="D14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2868
+</t>
+        </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -2038,28 +2297,30 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2081,108 +2342,137 @@
       <c r="C15" s="3" t="n">
         <v/>
       </c>
-      <c r="D15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2206,97 +2496,138 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11988
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0909
+</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11139
+</t>
+        </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11910
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9006
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9808
+</t>
+        </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9200
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22812
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2662
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1528
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">3048
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2315,132 +2646,144 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">1001
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9106
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v/>
-      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11282
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">522
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2993
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2459,113 +2802,143 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 1
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1804
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1146
+</t>
+        </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1604
-</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v/>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2587,100 +2960,135 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">17 6
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
       </c>
       <c r="P19" s="3" t="n">
         <v/>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29481
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">340
+</t>
+        </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11495
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2702,77 +3110,122 @@
       <c r="C20" s="3" t="n">
         <v/>
       </c>
-      <c r="D20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
         <v/>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11174
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
@@ -2780,12 +3233,15 @@
 </t>
         </is>
       </c>
-      <c r="Y20" s="3" t="n">
-        <v/>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2807,87 +3263,138 @@
       <c r="C21" s="3" t="n">
         <v/>
       </c>
-      <c r="D21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
       </c>
       <c r="Q21" s="3" t="n">
         <v/>
       </c>
-      <c r="R21" s="3" t="n">
-        <v/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9485
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590
+</t>
+        </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2909,77 +3416,123 @@
       <c r="C22" s="3" t="n">
         <v/>
       </c>
-      <c r="D22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -2988,13 +3541,13 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -3013,36 +3566,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1956
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -3052,69 +3620,92 @@
 </t>
         </is>
       </c>
-      <c r="L23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9268
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11804
+</t>
+        </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2679
+</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">22161
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -3133,134 +3724,144 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19456
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t xml:space="preserve">281
+</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11034
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10804
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12678
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3279,104 +3880,125 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 1 5
+</t>
+        </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1028
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1569
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
+</t>
+        </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">12218
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
@@ -3386,11 +4008,8 @@
       <c r="Y25" s="3" t="n">
         <v/>
       </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
+      <c r="Z25" s="3" t="n">
+        <v/>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -3407,101 +4026,148 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">385
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -3518,70 +4184,98 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1889
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
@@ -3591,24 +4285,33 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
       </c>
       <c r="Y27" s="3" t="n">
         <v/>
@@ -3634,83 +4337,128 @@
       <c r="C28" s="3" t="n">
         <v/>
       </c>
-      <c r="D28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="F28" s="3" t="n">
         <v/>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52940
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2207
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">567
+</t>
+        </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
       </c>
       <c r="Y28" s="3" t="n">
         <v/>
@@ -3736,86 +4484,143 @@
       <c r="C29" s="3" t="n">
         <v/>
       </c>
-      <c r="D29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6595
+</t>
+        </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3835,108 +4640,141 @@
       <c r="C30" s="3" t="n">
         <v/>
       </c>
-      <c r="D30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19524
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18168
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1310
+</t>
+        </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">20161
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26814
+</t>
+        </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">8365
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4200
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1320
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2989
+</t>
+        </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18182
+</t>
+        </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9856
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3162
+</t>
+        </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -3955,116 +4793,144 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13098
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28100
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">23183
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4083,113 +4949,146 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2189
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">568
+</t>
+        </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v/>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4206,121 +5105,141 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t xml:space="preserve">286
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4200
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">750
 </t>
         </is>
       </c>
@@ -4345,86 +5264,131 @@
       <c r="C34" s="3" t="n">
         <v/>
       </c>
-      <c r="D34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12846
+</t>
+        </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
       </c>
       <c r="Y34" s="3" t="n">
         <v/>
@@ -4447,90 +5411,135 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11908
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v/>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4555,83 +5564,142 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v/>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
       </c>
       <c r="Z36" s="3" t="n">
         <v/>
@@ -4654,92 +5722,143 @@
       <c r="C37" s="3" t="n">
         <v/>
       </c>
-      <c r="D37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8080
+</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218164
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">905
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10822
+</t>
+        </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">49208
+</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11022
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1098
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1068
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2312
+</t>
+        </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -4761,113 +5880,138 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11308
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8924208
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
+</t>
+        </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">387
+</t>
+        </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71481
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39312
-</t>
-        </is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v/>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -4884,113 +6028,140 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9421
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8986
+</t>
+        </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">408
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
       </c>
       <c r="Z39" s="3" t="n">
         <v/>
@@ -5010,44 +6181,77 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
@@ -5055,35 +6259,47 @@
 </t>
         </is>
       </c>
-      <c r="P40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v/>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -5093,13 +6309,13 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -5121,94 +6337,141 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8401
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
         <v/>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">623
+</t>
+        </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11084
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">765
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -5225,55 +6488,92 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
       </c>
       <c r="H42" s="3" t="n">
         <v/>
       </c>
-      <c r="I42" s="3" t="n">
-        <v/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>85401</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
@@ -5284,26 +6584,47 @@
       <c r="S42" s="3" t="n">
         <v/>
       </c>
-      <c r="T42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v/>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -5323,26 +6644,40 @@
       <c r="C43" s="3" t="n">
         <v/>
       </c>
-      <c r="D43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -5350,62 +6685,101 @@
 </t>
         </is>
       </c>
-      <c r="K43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8094
+</t>
+        </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1299
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v/>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -5427,24 +6801,27 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">8181
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11120
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1800
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -5452,41 +6829,48 @@
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v/>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -5502,8 +6886,11 @@
 </t>
         </is>
       </c>
-      <c r="S44" s="3" t="n">
-        <v/>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
@@ -5511,17 +6898,29 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
@@ -5547,21 +6946,33 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0221
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2884
+</t>
+        </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
@@ -5573,7 +6984,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -5585,13 +6996,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">11896
 </t>
         </is>
       </c>
@@ -5601,11 +7012,17 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11027
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179926
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -5615,19 +7032,25 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16560
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">16620
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
@@ -5637,18 +7060,27 @@
 </t>
         </is>
       </c>
-      <c r="V45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v/>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3228
+</t>
+        </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">644
 </t>
         </is>
       </c>
@@ -5675,16 +7107,19 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2719
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -5696,13 +7131,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -5721,11 +7156,17 @@
 </t>
         </is>
       </c>
-      <c r="M46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v/>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1854
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
@@ -5739,8 +7180,11 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
@@ -5748,20 +7192,29 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
@@ -5771,13 +7224,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -677,11 +677,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v/>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -709,7 +706,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -731,12 +728,15 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="3" t="n">
-        <v/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -754,13 +754,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1 39
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -772,7 +772,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -871,13 +871,13 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -893,11 +893,8 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
+      <c r="P5" s="3" t="n">
+        <v/>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -919,7 +916,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -937,7 +934,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -949,7 +946,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -979,7 +976,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1026,7 +1023,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1050,7 +1047,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1074,7 +1071,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
@@ -1144,11 +1141,8 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v/>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -1170,7 +1164,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1182,13 +1176,14 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">074
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1203,8 +1198,11 @@
 </t>
         </is>
       </c>
-      <c r="P7" s="3" t="n">
-        <v/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
@@ -1220,12 +1218,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -1237,8 +1236,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1249,19 +1247,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1285,7 +1283,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -1293,7 +1291,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1305,13 +1303,13 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1323,7 +1321,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1371,7 +1369,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">450
+          <t xml:space="preserve">459
 </t>
         </is>
       </c>
@@ -1383,7 +1381,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1438,15 +1436,12 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1152
-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v/>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1458,13 +1453,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
@@ -1482,19 +1476,19 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
@@ -1506,49 +1500,49 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20991
+          <t xml:space="preserve">2631
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1560,7 +1554,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6150
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
@@ -1584,87 +1578,88 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1679,7 +1674,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1709,7 +1704,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
@@ -1739,14 +1734,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1757,8 +1750,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1769,8 +1761,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1793,7 +1784,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -1805,7 +1796,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8909
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1817,7 +1808,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1835,7 +1826,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
@@ -1872,15 +1863,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v/>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1940,7 +1928,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1958,13 +1946,13 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1976,7 +1964,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -1997,7 +1985,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2009,7 +1997,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2028,94 +2016,93 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 1
-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v/>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2835
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -2124,24 +2111,25 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -2159,15 +2147,11 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v/>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -2201,20 +2185,16 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v/>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2225,7 +2205,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -2249,7 +2229,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -2267,7 +2247,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2868
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2279,7 +2259,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2291,7 +2271,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -2303,7 +2283,8 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>034</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2314,7 +2295,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2356,7 +2337,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2838
 </t>
         </is>
       </c>
@@ -2389,7 +2370,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2407,13 +2388,14 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2496,15 +2478,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11988
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0909
-</t>
-        </is>
+          <t xml:space="preserve">10388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v/>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2520,22 +2499,21 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">906
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9006
-</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2544,8 +2522,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2556,36 +2533,33 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t xml:space="preserve">904
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v/>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22812
+          <t xml:space="preserve">8382
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -2603,31 +2577,30 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1528
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3048
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2646,15 +2619,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v/>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2678,37 +2648,37 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2717,13 +2687,13 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2735,7 +2705,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2753,7 +2723,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2765,19 +2735,18 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">604
 </t>
         </is>
       </c>
@@ -2802,39 +2771,31 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 1
-</t>
-        </is>
+      <c r="C18" s="3" t="n">
+        <v/>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v/>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2846,25 +2807,24 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -2876,31 +2836,31 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">5298
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2918,8 +2878,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2955,8 +2914,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -2978,13 +2940,13 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 6
+          <t xml:space="preserve">17 5
 </t>
         </is>
       </c>
@@ -3002,7 +2964,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -3014,7 +2976,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3026,8 +2988,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>701</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
@@ -3035,7 +2996,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -3053,18 +3014,19 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -3082,13 +3044,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3112,7 +3074,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3139,7 +3101,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -3151,7 +3113,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3163,7 +3125,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3211,8 +3173,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3235,7 +3196,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -3265,7 +3226,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3277,7 +3238,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3301,19 +3262,19 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3325,7 +3286,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3358,13 +3319,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3382,13 +3343,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -3418,19 +3378,19 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3508,7 +3468,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3526,7 +3486,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -3536,12 +3496,14 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="n">
-        <v/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3566,15 +3528,12 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v/>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3586,31 +3545,30 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">5295
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3622,7 +3580,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3634,49 +3592,48 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11804
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679
+          <t xml:space="preserve">82678
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>976</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3687,25 +3644,24 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22161
-</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3724,11 +3680,8 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v/>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -3744,19 +3697,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2375
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -3772,8 +3725,11 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3831,7 +3787,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3849,7 +3805,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3880,26 +3836,24 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8 1 5
-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v/>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3911,13 +3865,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3929,45 +3883,42 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12218
-</t>
-        </is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v/>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
@@ -3977,8 +3928,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -3992,13 +3942,13 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4028,7 +3978,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4040,37 +3990,37 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4092,14 +4042,12 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
+      <c r="N26" s="3" t="n">
+        <v/>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4135,13 +4083,12 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>438</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">2494
 </t>
         </is>
       </c>
@@ -4159,14 +4106,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4186,25 +4132,25 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4216,7 +4162,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4228,13 +4174,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4252,13 +4198,13 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4268,8 +4214,10 @@
 </t>
         </is>
       </c>
-      <c r="Q27" s="3" t="n">
-        <v/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
@@ -4285,7 +4233,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -4339,18 +4287,21 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -4390,31 +4341,31 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52940
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4426,7 +4377,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4486,7 +4437,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4576,20 +4527,19 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -4606,7 +4556,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4637,48 +4587,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19524
+          <t xml:space="preserve">13348
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18168
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20161
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26814
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -4696,25 +4649,23 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8365
+          <t xml:space="preserve">1854
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
-</t>
+          <t>434644</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4726,7 +4677,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
@@ -4744,38 +4695,35 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18182
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162
+          <t xml:space="preserve">31362
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4795,7 +4743,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4831,7 +4779,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4841,12 +4789,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85 2
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -4924,8 +4875,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
-</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4949,33 +4899,27 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v/>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v/>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5023,68 +4967,65 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>714</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1946
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n">
@@ -5105,21 +5046,18 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="C33" s="3" t="n">
+        <v/>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5143,13 +5081,13 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5167,13 +5105,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5185,19 +5123,18 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5227,7 +5164,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -5266,7 +5203,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -5278,13 +5215,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -5332,7 +5269,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5344,13 +5281,13 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5374,7 +5311,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5386,7 +5323,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -5413,7 +5350,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5431,7 +5368,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5449,7 +5386,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5485,25 +5422,25 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11908
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5533,7 +5470,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5564,27 +5501,24 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v/>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5602,7 +5536,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5626,7 +5560,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">072
 </t>
         </is>
       </c>
@@ -5674,7 +5608,8 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5724,13 +5659,13 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">8 82
 </t>
         </is>
       </c>
@@ -5742,62 +5677,60 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">4986
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8080
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218164
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5808,26 +5741,25 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2086
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>447</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5838,7 +5770,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5850,13 +5782,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1068
+          <t xml:space="preserve">1560
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -5916,13 +5848,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5934,7 +5866,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -5970,13 +5902,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">387
+          <t xml:space="preserve">577
 </t>
         </is>
       </c>
@@ -5988,8 +5919,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -6028,126 +5958,120 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v/>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8986
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6159,7 +6083,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -6183,13 +6107,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6201,19 +6125,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3164
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6223,15 +6147,12 @@
 </t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
+      <c r="J40" s="3" t="n">
+        <v/>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
@@ -6261,19 +6182,19 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6285,7 +6206,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
@@ -6339,13 +6260,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -6363,7 +6284,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6375,8 +6296,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6387,7 +6307,8 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">58
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6398,13 +6319,13 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6429,18 +6350,21 @@
 </t>
         </is>
       </c>
-      <c r="S41" s="3" t="n">
-        <v/>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -6458,7 +6382,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -6488,11 +6412,8 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v/>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -6508,8 +6429,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6518,8 +6438,11 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="n">
-        <v/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
@@ -6527,11 +6450,8 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
+      <c r="J42" s="3" t="n">
+        <v/>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -6553,7 +6473,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6577,8 +6497,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
@@ -6604,13 +6523,13 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6622,7 +6541,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6646,20 +6565,18 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v/>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -6669,13 +6586,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6723,7 +6640,7 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8094
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -6735,31 +6652,30 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6796,24 +6712,27 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8181
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
@@ -6831,31 +6750,33 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="J44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -6870,7 +6791,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6898,11 +6819,8 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1236
-</t>
-        </is>
+      <c r="U44" s="3" t="n">
+        <v/>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
@@ -6912,8 +6830,7 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -6946,40 +6863,36 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v/>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">8306
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6990,19 +6903,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">10896
 </t>
         </is>
       </c>
@@ -7014,15 +6927,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11027
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179926
-</t>
-        </is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v/>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -7032,20 +6942,17 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16620
-</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -7062,19 +6969,19 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">1 8
 </t>
         </is>
       </c>
@@ -7107,8 +7014,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2719
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -7119,7 +7025,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -7131,13 +7037,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -7158,13 +7064,13 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -7182,7 +7088,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -7194,7 +7100,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -7206,7 +7112,7 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -7230,7 +7136,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">16 54
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -682,34 +682,34 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9230
+</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">68
@@ -730,63 +730,60 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v/>
       </c>
       <c r="V4" s="3" t="n">
         <v/>
@@ -818,8 +815,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -865,79 +865,82 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -946,7 +949,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">565
 </t>
         </is>
       </c>
@@ -971,12 +974,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -988,7 +994,8 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1041,7 +1048,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -1071,7 +1078,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1083,7 +1090,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1126,8 +1133,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -1141,8 +1151,11 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
-        <v/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -1164,7 +1177,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1176,13 +1189,13 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">074
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1194,7 +1207,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1206,7 +1219,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">3004
 </t>
         </is>
       </c>
@@ -1224,19 +1237,20 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1247,7 +1261,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
@@ -1259,7 +1273,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1283,33 +1297,37 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">92359
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1325,12 +1343,15 @@
 </t>
         </is>
       </c>
-      <c r="L8" s="3" t="n">
-        <v/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1346,8 +1367,11 @@
 </t>
         </is>
       </c>
-      <c r="P8" s="3" t="n">
-        <v/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1369,40 +1393,43 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">420
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -1426,106 +1453,109 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1488
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8871
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">348
+</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4235
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">917
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
-</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4235
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">11960
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2631
+          <t xml:space="preserve">92551
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1536,25 +1566,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9714
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2299
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -1578,7 +1608,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1596,7 +1626,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1614,13 +1644,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1668,13 +1698,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1704,13 +1734,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">5 9
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1734,12 +1764,13 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1750,18 +1781,18 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>546</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1796,7 +1827,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -1808,7 +1839,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -1820,30 +1851,40 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v/>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">489
+</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="n">
         <v/>
@@ -1863,12 +1904,15 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1880,7 +1924,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">431
 </t>
         </is>
       </c>
@@ -1922,7 +1966,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1940,7 +1984,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1964,40 +2008,39 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2571
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2021,40 +2064,40 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">60
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -2063,7 +2106,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -2087,13 +2130,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2111,19 +2154,19 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2135,7 +2178,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2147,11 +2190,15 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>7640</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -2189,12 +2236,16 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
-        <v/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2205,7 +2256,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -2229,13 +2280,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -2253,31 +2304,31 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2295,7 +2346,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2337,7 +2388,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2838
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2365,12 +2416,15 @@
 </t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
-        <v/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -2388,13 +2442,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2424,7 +2478,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2436,7 +2490,7 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2448,13 +2502,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2473,21 +2527,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10388
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11139
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2499,19 +2559,18 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t xml:space="preserve">2882
+</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2522,7 +2581,8 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2533,21 +2593,24 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">9094
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8382
+          <t xml:space="preserve">1382
 </t>
         </is>
       </c>
@@ -2565,8 +2628,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2589,7 +2651,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>953</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2600,7 +2662,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2624,7 +2686,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2642,13 +2704,13 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2681,7 +2743,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2693,31 +2755,31 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
@@ -2735,24 +2797,25 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
+          <t xml:space="preserve">10685
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">810 8
 </t>
         </is>
       </c>
@@ -2771,55 +2834,56 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>496</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2830,14 +2894,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2848,14 +2910,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2866,38 +2926,41 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">007
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">380
+</t>
+        </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2914,11 +2977,8 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="C19" s="3" t="n">
+        <v/>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2994,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -2946,7 +3006,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2964,7 +3024,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2982,21 +3042,25 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
@@ -3014,7 +3078,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -3044,13 +3108,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2940
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3069,8 +3133,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -3090,18 +3157,21 @@
 </t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
-        <v/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3113,7 +3183,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -3167,13 +3237,14 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>760</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3196,13 +3267,13 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3226,7 +3297,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -3262,19 +3333,18 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3286,7 +3356,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -3302,8 +3372,11 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
@@ -3319,13 +3392,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -3337,18 +3410,19 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3373,8 +3447,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -3384,13 +3461,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -3426,7 +3503,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3438,7 +3515,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3462,13 +3539,13 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -3486,19 +3563,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3509,7 +3586,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">2549
 </t>
         </is>
       </c>
@@ -3528,12 +3605,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3545,30 +3625,30 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>848</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295
-</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -3580,42 +3660,43 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">1404
+</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
@@ -3627,41 +3708,40 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82678
-</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>976</t>
+          <t xml:space="preserve">919
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">11235
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">9356
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>70501</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">6528
 </t>
         </is>
       </c>
@@ -3697,7 +3777,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2375
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3709,49 +3789,46 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">054
 </t>
         </is>
       </c>
@@ -3763,7 +3840,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">2841
 </t>
         </is>
       </c>
@@ -3781,43 +3858,43 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3836,36 +3913,36 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v/>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19 4
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3889,36 +3966,35 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">076
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v/>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
@@ -3928,13 +4004,12 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="U25" s="3" t="n">
@@ -3948,18 +4023,25 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -3976,39 +4058,36 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v/>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -4020,7 +4099,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -4042,18 +4121,21 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="n">
-        <v/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -4077,18 +4159,19 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">522
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4106,13 +4189,14 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">1128
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4130,27 +4214,24 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v/>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -4162,49 +4243,49 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -4216,7 +4297,8 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -4233,19 +4315,19 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -4261,11 +4343,17 @@
 </t>
         </is>
       </c>
-      <c r="Y27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v/>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -4282,24 +4370,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -4311,7 +4402,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
@@ -4323,13 +4414,13 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4341,19 +4432,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -4383,7 +4474,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
@@ -4395,27 +4486,33 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -4432,69 +4529,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -4527,19 +4627,20 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -4556,7 +4657,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4587,15 +4688,12 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v/>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13348
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
@@ -4607,60 +4705,57 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">095
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
-</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">2800
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
-</t>
+          <t>94348</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>434644</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4695,35 +4790,35 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>704</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31362
+          <t xml:space="preserve">9162
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>476</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4743,7 +4838,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4767,13 +4862,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4789,15 +4884,12 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85 2
-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4809,13 +4901,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">2051
 </t>
         </is>
       </c>
@@ -4833,16 +4925,16 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">598
@@ -4851,7 +4943,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4875,12 +4967,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4904,12 +4997,14 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -4925,8 +5020,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4937,13 +5031,13 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4959,77 +5053,69 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
+      <c r="N32" s="3" t="n">
+        <v/>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
+          <t xml:space="preserve">048
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v/>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>548</t>
+          <t xml:space="preserve">968
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v/>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">44 128
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -5051,19 +5137,19 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -5087,7 +5173,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5105,13 +5191,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5129,7 +5215,8 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -5140,19 +5227,19 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5164,7 +5251,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5180,8 +5267,11 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="3" t="n">
-        <v/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -5203,112 +5293,112 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">482
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -5327,11 +5417,17 @@
 </t>
         </is>
       </c>
-      <c r="Y34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v/>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">670
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -5348,33 +5444,30 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v/>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5404,13 +5497,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5422,25 +5515,25 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5452,7 +5545,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5470,7 +5563,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">10188
 </t>
         </is>
       </c>
@@ -5480,11 +5573,17 @@
 </t>
         </is>
       </c>
-      <c r="Y35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v/>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5506,19 +5605,19 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5554,13 +5653,13 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">072
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -5590,7 +5689,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -5602,13 +5701,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5632,7 +5731,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -5659,49 +5758,48 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 82
+          <t xml:space="preserve">88218
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4986
+          <t xml:space="preserve">456
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109
-</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1172
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -5712,54 +5810,53 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">1318
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">10822
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5770,19 +5867,19 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">9981
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1560
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -5830,7 +5927,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5848,15 +5945,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -5866,13 +5960,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5902,12 +5996,13 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5919,29 +6014,33 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">12790 1
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -5958,18 +6057,21 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>436</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5980,36 +6082,32 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -6021,52 +6119,51 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v/>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -6083,12 +6180,14 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -6105,96 +6204,96 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v/>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1080
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6206,13 +6305,13 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
@@ -6260,32 +6359,31 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -6296,7 +6394,8 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6319,13 +6418,13 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6335,8 +6434,11 @@
 </t>
         </is>
       </c>
-      <c r="P41" s="3" t="n">
-        <v/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
@@ -6346,7 +6448,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6358,19 +6460,19 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -6382,20 +6484,18 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v/>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -6417,7 +6517,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1486
 </t>
         </is>
       </c>
@@ -6429,29 +6529,33 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2201
+</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">654
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -6461,19 +6565,19 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6497,11 +6601,15 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
@@ -6535,13 +6643,13 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6565,43 +6673,46 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1501
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11744
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1185
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6610,90 +6721,91 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0250
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">570
-</t>
-        </is>
-      </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6714,51 +6826,52 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6779,31 +6892,31 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">1548
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -6819,8 +6932,11 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="n">
-        <v/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
@@ -6830,7 +6946,8 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -6845,8 +6962,11 @@
 </t>
         </is>
       </c>
-      <c r="Z44" s="3" t="n">
-        <v/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6868,54 +6988,55 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11658
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8306
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>951</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">594
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896
+          <t xml:space="preserve">1096
 </t>
         </is>
       </c>
@@ -6927,12 +7048,15 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4990
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -6942,57 +7066,63 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11911
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">5179
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">15430
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">3929
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111411
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7014,7 +7144,8 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>619</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -7025,13 +7156,13 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -7053,8 +7184,11 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72162 8
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7070,78 +7204,81 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">5549
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">831
 </t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="Y46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">36
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16 54
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -682,104 +682,87 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="U4" s="3" t="n">
@@ -817,146 +800,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>565</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -976,146 +935,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1135,146 +1070,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1297,140 +1208,117 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92359
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1453,104 +1341,87 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871
-</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
-</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11960
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92551
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1560,32 +1431,27 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9714
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1608,140 +1474,117 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 9
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1764,8 +1607,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1775,8 +1617,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1791,62 +1632,52 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -1861,8 +1692,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1882,8 +1712,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>589</t>
         </is>
       </c>
       <c r="Z11" s="3" t="n">
@@ -1906,116 +1735,97 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -2040,8 +1850,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2064,140 +1873,117 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2220,140 +2006,117 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2376,140 +2139,117 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2529,38 +2269,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2575,26 +2309,22 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9094
-</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2604,26 +2334,22 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
-</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2633,20 +2359,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2656,14 +2379,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2686,44 +2407,37 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2731,92 +2445,77 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10685
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810 8
-</t>
+          <t>254 1</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2836,14 +2535,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2888,8 +2585,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2904,8 +2600,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2920,8 +2615,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2946,20 +2640,17 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">007
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2982,140 +2673,117 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2940
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3135,146 +2803,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
+          <t>475</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3297,38 +2941,32 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3338,98 +2976,82 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3449,128 +3071,107 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3580,14 +3181,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3607,38 +3206,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3648,62 +3241,52 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>529</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3713,20 +3296,17 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
-</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9356
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
@@ -3741,8 +3321,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6528
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3765,44 +3344,37 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
@@ -3810,92 +3382,77 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">054
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3915,14 +3472,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -3930,50 +3485,42 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 4
-</t>
+          <t>19 2</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">076
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -3998,8 +3545,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -4017,8 +3563,7 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4033,14 +3578,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4063,140 +3606,117 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4214,145 +3734,124 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4372,146 +3871,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4531,146 +4006,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4693,20 +4144,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
-</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">095
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4716,8 +4164,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4727,8 +4174,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4743,14 +4189,12 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4760,38 +4204,32 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
-</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4801,8 +4239,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4812,8 +4249,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162
-</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4838,50 +4274,42 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4889,92 +4317,77 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2051
-</t>
+          <t>051</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4997,8 +4410,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5008,14 +4420,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -5025,32 +4435,27 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
@@ -5058,8 +4463,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -5077,14 +4481,12 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5102,14 +4504,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44 128
-</t>
+          <t>91 22</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -5137,140 +4537,117 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5293,140 +4670,117 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5449,140 +4803,117 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5605,134 +4936,112 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n">
@@ -5753,31 +5062,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88218
-</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5792,20 +5099,17 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5820,38 +5124,32 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
-</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
-</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5861,32 +5159,27 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
-</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5909,44 +5202,37 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
@@ -5954,92 +5240,77 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12790 1
-</t>
+          <t>11 1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6059,8 +5330,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6070,14 +5340,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -6095,38 +5363,32 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6146,14 +5408,12 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6168,20 +5428,17 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>645</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6209,134 +5466,112 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z40" s="3" t="n">
@@ -6359,26 +5594,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -6388,110 +5619,92 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n">
@@ -6517,140 +5730,117 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1486
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6673,140 +5863,117 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11744
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6826,146 +5993,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6983,145 +6126,124 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11658
-</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">594
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
-</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15430
-</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111411
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7144,140 +6266,117 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72162 8
-</t>
+          <t>5 18</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5549
-</t>
+          <t>51 1</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>081 1</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>842</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>254 1</t>
+          <t>90 21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>001</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>136</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>256</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>142</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>91 22</t>
+          <t>91 191</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -4798,8 +4798,10 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -4828,7 +4830,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -5064,7 +5066,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5139,12 +5141,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5164,12 +5166,12 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>950</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5222,7 +5224,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -5260,7 +5262,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5295,12 +5297,12 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>11 1</t>
+          <t>011 1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -5310,7 +5312,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5624,7 +5626,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5679,7 +5681,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5689,7 +5691,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -5704,7 +5706,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n">
@@ -5740,7 +5742,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5770,7 +5772,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5873,7 +5875,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5928,7 +5930,7 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
@@ -5938,12 +5940,12 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -5993,12 +5995,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -6008,7 +6010,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6018,12 +6020,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -6053,7 +6055,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6063,7 +6065,7 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -6128,7 +6130,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6163,7 +6165,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6183,12 +6185,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6208,12 +6210,12 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6233,7 +6235,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6301,7 +6303,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>5 18</t>
+          <t>28 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6316,7 +6318,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>51 1</t>
+          <t>2011 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6326,7 +6328,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6376,7 +6378,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_pre_QA_QC.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>318</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>081 1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>892</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>107</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>90 21</t>
+          <t>08 8</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>00</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>595</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>572</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>208</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>91 191</t>
+          <t>00 10</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -4798,10 +4798,8 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v/>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -5076,7 +5074,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5146,7 +5144,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5171,7 +5169,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>014</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5262,7 +5260,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5282,32 +5280,32 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>05 0</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
           <t>01</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>011 1</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5478,7 +5476,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5553,7 +5551,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5596,7 +5594,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5626,7 +5624,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5681,7 +5679,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>628</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5706,7 +5704,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n">
@@ -5960,7 +5958,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>290</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5995,7 +5993,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -6020,7 +6018,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -6055,7 +6053,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6110,7 +6108,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6130,7 +6128,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6165,7 +6163,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>615</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6185,7 +6183,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6230,7 +6228,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6303,7 +6301,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>28 08</t>
+          <t>2 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6318,7 +6316,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>2011 0</t>
+          <t>200 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6328,7 +6326,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
